--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-07-29 12:07</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-07-30 06:06</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-07-30 06:06</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-07-31 06:29</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-07-31 06:29</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-01 06:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-01 06:14</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-02 06:17</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-02 06:17</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-03 06:44</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-03 06:44</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-04 06:10</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-04 06:10</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-05 06:06</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-05 06:06</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-06 06:10</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-06 06:10</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-07 05:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-07 05:13</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-08 04:35</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-08 04:35</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-09 04:45</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-09 04:45</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-10 05:06</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-10 05:06</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-11 04:49</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-11 04:49</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-12 05:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-12 05:14</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-13 05:17</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-13 05:17</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-14 05:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-14 05:14</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-15 04:04</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-15 04:04</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-16 04:07</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-16 04:07</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-17 04:11</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-17 04:11</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-18 04:07</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-18 04:07</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-19 04:08</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-19 04:08</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-20 04:07</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-20 04:07</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-21 04:09</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-21 04:09</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-22 04:05</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-22 04:05</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-23 04:09</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-23 04:09</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-24 04:14</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-24 04:14</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-25 04:08</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-25 04:08</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-26 04:10</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-26 04:10</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-27 14:26</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-27 14:26</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-28 15:34</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-28 15:34</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-29 10:18</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-29 10:18</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-30 09:24</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-30 09:24</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-31 09:59</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-08-31 09:59</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-01 08:50</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-01 08:50</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-02 08:03</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-02 08:03</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-03 08:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-03 08:13</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-04 08:08</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-04 08:08</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-05 07:48</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-05 07:48</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-06 08:02</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-06 08:02</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-07 08:33</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-07 08:33</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-08 08:16</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-08 08:16</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-09 08:19</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-09 08:19</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-10 08:18</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-10 08:18</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-11 08:13</t>
         </is>
       </c>
     </row>

--- a/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
+++ b/Test Results/Excel/k6_Load_Test_Report_LATEST.xlsx
@@ -588,7 +588,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-11 08:13</t>
+          <t>Profile: 100 Concurrent Virtual Users × 60s Duration  |  Target: https://rhema5.github.io/trustroute-PDD/  |  Date: 2026-09-12 08:04</t>
         </is>
       </c>
     </row>
